--- a/solution/task4/answer/task4_paper_table.xlsx
+++ b/solution/task4/answer/task4_paper_table.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表6" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="表6" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -457,16 +457,16 @@
         <v>6</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1.9493</v>
+        <v>1.7195</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1.78</v>
+        <v>1.5377</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1.2555</v>
+        <v>1.0226</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.5682</v>
+        <v>0.4207</v>
       </c>
     </row>
     <row r="3">
@@ -474,16 +474,16 @@
         <v>12</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0.8691</v>
+        <v>0.7376</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.7727000000000001</v>
+        <v>0.6545</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.4841</v>
+        <v>0.4083</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.2141</v>
+        <v>0.1669</v>
       </c>
     </row>
     <row r="4">
@@ -491,16 +491,16 @@
         <v>18</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.4567</v>
+        <v>0.4087</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.4108</v>
+        <v>0.3686</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.264</v>
+        <v>0.2397</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.1017</v>
+        <v>0.0892</v>
       </c>
     </row>
     <row r="5">
@@ -508,16 +508,16 @@
         <v>24</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.3056</v>
+        <v>0.2851</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.2791</v>
+        <v>0.261</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.1894</v>
+        <v>0.179</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.0711</v>
+        <v>0.0673</v>
       </c>
     </row>
     <row r="6">
@@ -525,16 +525,16 @@
         <v>30</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.2369</v>
+        <v>0.2263</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.2188</v>
+        <v>0.2094</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.1549</v>
+        <v>0.1493</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.0608</v>
+        <v>0.0595</v>
       </c>
     </row>
     <row r="7">
@@ -542,16 +542,16 @@
         <v>36</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.1991</v>
+        <v>0.1928</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.1853</v>
+        <v>0.1796</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.1351</v>
+        <v>0.1317</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.0565</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="8">
@@ -559,16 +559,16 @@
         <v>42</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.1754</v>
+        <v>0.1712</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.1641</v>
+        <v>0.1604</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.1222</v>
+        <v>0.12</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.0543</v>
+        <v>0.0541</v>
       </c>
     </row>
     <row r="9">
@@ -576,22 +576,22 @@
         <v>48</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0.159</v>
+        <v>0.1561</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0.1494</v>
+        <v>0.1468</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.1132</v>
+        <v>0.1116</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.0531</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>烘干结束时间（52.3709 h）</t>
+          <t>烘干结束时间（51.0874 h）</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -604,7 +604,7 @@
         <v>0.1081</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.0525</v>
+        <v>0.0526</v>
       </c>
     </row>
     <row r="12">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>52.3709</v>
+        <v>51.0874</v>
       </c>
     </row>
   </sheetData>
